--- a/progress/metrics_metadata.xlsx
+++ b/progress/metrics_metadata.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Name</t>
   </si>
@@ -27,6 +27,9 @@
     <t>Unit</t>
   </si>
   <si>
+    <t>Source</t>
+  </si>
+  <si>
     <t>frac_crop</t>
   </si>
   <si>
@@ -36,6 +39,9 @@
     <t>%</t>
   </si>
   <si>
+    <t>GLC_FCS30D</t>
+  </si>
+  <si>
     <t>frac_grassland</t>
   </si>
   <si>
@@ -64,6 +70,39 @@
   </si>
   <si>
     <t xml:space="preserve">Shannon index of the 1km land cover calculated on the simplified 15 classes identified as the tens digits in GLC_FCS30D</t>
+  </si>
+  <si>
+    <t>mean_average_temperature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">average monthly temperature in the ten years period before the year of sampling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">degree celsius</t>
+  </si>
+  <si>
+    <t>easyclimate</t>
+  </si>
+  <si>
+    <t>mean_average_precipitation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">average annual precipitation in the ten years period before the year of sampling</t>
+  </si>
+  <si>
+    <t>mm</t>
+  </si>
+  <si>
+    <t>mean_summer_temperature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">average summer temperature in the ten years period before the year of sampling</t>
+  </si>
+  <si>
+    <t>mean_spring_precipitation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">average spring precipitation in the ten years period before the year of sampling</t>
   </si>
 </sst>
 </file>
@@ -105,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
@@ -118,6 +157,10 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -617,9 +660,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" min="1" max="1" width="15.640625"/>
+    <col bestFit="1" min="1" max="1" width="25.421875"/>
     <col customWidth="1" min="2" max="2" width="78.57421875"/>
-    <col bestFit="1" min="3" max="3" width="4.421875"/>
+    <col bestFit="1" min="3" max="3" width="12.78125"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
@@ -632,68 +675,145 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2" ht="28.5">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3" ht="28.5">
       <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="D3" t="s">
         <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="4" ht="42.75">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5" ht="28.5">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6" ht="156.75">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C6" s="2"/>
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="7" ht="28.5">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C7" s="2"/>
+      <c r="D7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25">
+      <c r="A8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25">
+      <c r="A9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="A10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25">
+      <c r="A11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>21</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
